--- a/data/trans_bre/P57_AC_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P57_AC_R-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 6,35</t>
+          <t>-7,42; 6,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 11,5</t>
+          <t>-3,46; 11,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 7,0</t>
+          <t>-5,24; 7,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 2,02</t>
+          <t>-10,96; 1,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 9,89</t>
+          <t>-10,92; 10,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 19,51</t>
+          <t>-5,18; 18,51</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 9,73</t>
+          <t>-6,69; 9,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 3,87</t>
+          <t>-18,6; 2,83</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 11,31</t>
+          <t>-3,29; 11,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 11,61</t>
+          <t>-3,4; 11,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 10,58</t>
+          <t>-2,57; 10,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 6,97</t>
+          <t>-5,53; 7,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 19,51</t>
+          <t>-5,11; 19,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 18,7</t>
+          <t>-4,94; 18,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 14,77</t>
+          <t>-3,41; 14,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 11,97</t>
+          <t>-8,27; 13,16</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 6,69</t>
+          <t>-9,24; 6,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 10,86</t>
+          <t>-2,71; 11,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 7,66</t>
+          <t>-4,67; 8,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 53,63</t>
+          <t>0,18; 52,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 9,74</t>
+          <t>-12,61; 8,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 16,7</t>
+          <t>-3,97; 17,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 9,43</t>
+          <t>-5,38; 10,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 393,25</t>
+          <t>0,7; 295,03</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 6,83</t>
+          <t>-1,94; 7,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 13,99</t>
+          <t>5,63; 14,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,2</t>
+          <t>0,73; 7,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 2,43</t>
+          <t>-6,71; 2,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 9,74</t>
+          <t>-2,69; 10,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,14; 21,2</t>
+          <t>8,08; 21,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,52</t>
+          <t>0,91; 10,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 3,93</t>
+          <t>-10,15; 3,73</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 13,07</t>
+          <t>0,57; 12,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 10,4</t>
+          <t>-0,03; 10,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 8,49</t>
+          <t>0,37; 8,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 2,18</t>
+          <t>-22,44; 2,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 19,7</t>
+          <t>0,81; 19,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 15,61</t>
+          <t>-0,07; 15,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 10,98</t>
+          <t>0,47; 10,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 3,23</t>
+          <t>-31,38; 3,78</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,55; 19,18</t>
+          <t>6,33; 18,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 17,65</t>
+          <t>4,81; 18,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 10,32</t>
+          <t>-0,35; 10,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,14; 33,28</t>
+          <t>10,01; 33,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,55; 38,11</t>
+          <t>10,22; 35,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,82; 32,78</t>
+          <t>7,45; 33,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 14,3</t>
+          <t>-0,48; 14,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,19; 106,77</t>
+          <t>18,82; 106,0</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,16</t>
+          <t>0,58; 5,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,06</t>
+          <t>4,46; 9,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,15</t>
+          <t>1,14; 4,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 17,72</t>
+          <t>-1,51; 17,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,74</t>
+          <t>0,82; 7,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,84</t>
+          <t>6,67; 14,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,65</t>
+          <t>1,44; 6,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 39,05</t>
+          <t>-2,46; 36,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_AC_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P57_AC_R-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,37</t>
+          <t>-4,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-7,87%</t>
+          <t>-7,45%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 6,48</t>
+          <t>-7,62; 6,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 11,32</t>
+          <t>-3,09; 11,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 7,37</t>
+          <t>-5,46; 6,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 1,51</t>
+          <t>-10,19; 1,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 10,52</t>
+          <t>-11,21; 10,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 18,51</t>
+          <t>-4,63; 19,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 9,83</t>
+          <t>-6,91; 9,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 2,83</t>
+          <t>-16,97; 3,55</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>-1,72%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 11,52</t>
+          <t>-3,76; 10,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 11,58</t>
+          <t>-2,07; 11,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 10,43</t>
+          <t>-2,62; 10,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 7,88</t>
+          <t>-7,05; 5,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 19,85</t>
+          <t>-5,65; 18,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 18,72</t>
+          <t>-3,14; 18,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 14,45</t>
+          <t>-3,43; 14,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 13,16</t>
+          <t>-10,54; 8,25</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25,96</t>
+          <t>1,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 6,01</t>
+          <t>-10,14; 5,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 11,02</t>
+          <t>-3,18; 10,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 8,46</t>
+          <t>-5,37; 7,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 52,37</t>
+          <t>-6,2; 8,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,61; 8,49</t>
+          <t>-13,65; 8,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 17,3</t>
+          <t>-4,75; 17,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 10,28</t>
+          <t>-6,2; 9,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 295,03</t>
+          <t>-9,54; 14,89</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-2,12</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-3,31%</t>
+          <t>-2,06%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 7,03</t>
+          <t>-1,64; 6,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 14,17</t>
+          <t>5,88; 14,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,95</t>
+          <t>0,89; 7,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 2,27</t>
+          <t>-5,46; 2,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 10,14</t>
+          <t>-2,28; 9,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,08; 21,5</t>
+          <t>8,5; 21,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 10,32</t>
+          <t>1,09; 10,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 3,73</t>
+          <t>-8,22; 4,61</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-6,82</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-10,0%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 12,81</t>
+          <t>0,9; 13,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 10,59</t>
+          <t>-0,1; 10,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 8,34</t>
+          <t>0,36; 8,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 2,51</t>
+          <t>-2,89; 7,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 19,07</t>
+          <t>1,17; 20,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 15,78</t>
+          <t>-0,13; 14,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 10,71</t>
+          <t>0,47; 10,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 3,78</t>
+          <t>-4,05; 11,64</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,22</t>
+          <t>19,94</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>44,64%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,33; 18,51</t>
+          <t>5,98; 18,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,81; 18,11</t>
+          <t>4,94; 18,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 10,69</t>
+          <t>-0,47; 10,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,01; 33,07</t>
+          <t>10,56; 30,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,22; 35,83</t>
+          <t>9,4; 35,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,45; 33,63</t>
+          <t>7,14; 33,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 14,98</t>
+          <t>-0,58; 15,2</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,82; 106,0</t>
+          <t>19,54; 86,28</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>1,62</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,11</t>
+          <t>0,55; 5,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,08</t>
+          <t>4,59; 9,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,92</t>
+          <t>1,02; 4,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 17,32</t>
+          <t>-0,94; 3,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,68</t>
+          <t>0,82; 7,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,67; 14,0</t>
+          <t>6,85; 13,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,33</t>
+          <t>1,27; 6,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 36,55</t>
+          <t>-1,49; 6,47</t>
         </is>
       </c>
     </row>
